--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.99686400491451</v>
+        <v>8.124490400798608</v>
       </c>
       <c r="D2" t="n">
-        <v>49.13803552229992</v>
+        <v>7.984930772373738</v>
       </c>
       <c r="E2" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.58151809503234</v>
+        <v>7.894496690442755</v>
       </c>
       <c r="D3" t="n">
-        <v>47.59569111004508</v>
+        <v>7.734299805382326</v>
       </c>
       <c r="E3" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.54140567525153</v>
+        <v>9.025478422228373</v>
       </c>
       <c r="D4" t="n">
-        <v>55.23572470226414</v>
+        <v>8.975805264117922</v>
       </c>
       <c r="E4" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.70037075329893</v>
+        <v>7.426310247411077</v>
       </c>
       <c r="D5" t="n">
-        <v>45.64564386094382</v>
+        <v>7.417417127403371</v>
       </c>
       <c r="E5" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.16730872637616</v>
+        <v>4.902187668036126</v>
       </c>
       <c r="D6" t="n">
-        <v>28.98529223426315</v>
+        <v>4.710109988067761</v>
       </c>
       <c r="E6" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F6" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.67510382307077</v>
+        <v>5.959704371249001</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51349256745756</v>
+        <v>5.770942542211854</v>
       </c>
       <c r="E7" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F7" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.46655770287855</v>
+        <v>4.950815626717764</v>
       </c>
       <c r="D8" t="n">
-        <v>30.85483223038725</v>
+        <v>5.013910237437929</v>
       </c>
       <c r="E8" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.01227218791486</v>
+        <v>1.789494230536165</v>
       </c>
       <c r="D9" t="n">
-        <v>10.15491009989899</v>
+        <v>1.650172891233587</v>
       </c>
       <c r="E9" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F9" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.83841203728722</v>
+        <v>4.686241956059173</v>
       </c>
       <c r="D10" t="n">
-        <v>29.62969088530814</v>
+        <v>4.814824768862572</v>
       </c>
       <c r="E10" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F10" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.50458308382414</v>
+        <v>4.956994751121423</v>
       </c>
       <c r="D11" t="n">
-        <v>29.90783976326467</v>
+        <v>4.860023961530509</v>
       </c>
       <c r="E11" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F11" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.39914373944362</v>
+        <v>2.502360857659589</v>
       </c>
       <c r="D12" t="n">
-        <v>16.48909255436174</v>
+        <v>2.679477540083783</v>
       </c>
       <c r="E12" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F12" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>18.5210061474143</v>
+        <v>3.009663498954823</v>
       </c>
       <c r="D13" t="n">
-        <v>19.13826043337138</v>
+        <v>3.109967320422849</v>
       </c>
       <c r="E13" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.592940581604</v>
+        <v>1.721352844510649</v>
       </c>
       <c r="D14" t="n">
-        <v>11.26986291928649</v>
+        <v>1.831352724384055</v>
       </c>
       <c r="E14" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F14" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.0540526561432</v>
+        <v>4.23378355662327</v>
       </c>
       <c r="D15" t="n">
-        <v>26.68004219646927</v>
+        <v>4.335506856926256</v>
       </c>
       <c r="E15" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F15" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.0073732208529</v>
+        <v>4.551198148388597</v>
       </c>
       <c r="D16" t="n">
-        <v>29.0737775998935</v>
+        <v>4.724488859982694</v>
       </c>
       <c r="E16" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>36.68269718313804</v>
+        <v>5.960938292259931</v>
       </c>
       <c r="D17" t="n">
-        <v>37.86370355740894</v>
+        <v>6.152851828078953</v>
       </c>
       <c r="E17" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F17" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.1389796224633</v>
+        <v>6.035084188650286</v>
       </c>
       <c r="D18" t="n">
-        <v>37.91311166162808</v>
+        <v>6.160880645014563</v>
       </c>
       <c r="E18" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F18" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>43.70834187179267</v>
+        <v>7.102605554166309</v>
       </c>
       <c r="D19" t="n">
-        <v>44.29793347363533</v>
+        <v>7.198414189465741</v>
       </c>
       <c r="E19" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F19" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>30.79135010902439</v>
+        <v>5.003594392716463</v>
       </c>
       <c r="D20" t="n">
-        <v>31.00554989073641</v>
+        <v>5.038401857244667</v>
       </c>
       <c r="E20" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F20" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>17.93090711657839</v>
+        <v>2.913772406443988</v>
       </c>
       <c r="D21" t="n">
-        <v>18.01078783853727</v>
+        <v>2.926753023762306</v>
       </c>
       <c r="E21" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F21" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>37.58913539651347</v>
+        <v>6.108234501933439</v>
       </c>
       <c r="D22" t="n">
-        <v>37.76714481692684</v>
+        <v>6.137161032750611</v>
       </c>
       <c r="E22" t="n">
-        <v>12.35139325274357</v>
+        <v>2.007101403570829</v>
       </c>
       <c r="F22" t="n">
-        <v>12.1422851139724</v>
+        <v>1.973121331020515</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
